--- a/Team-Data/2011-12/4-6-2011-12.xlsx
+++ b/Team-Data/2011-12/4-6-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,46 +728,46 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F2" t="n">
         <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>0.589</v>
+        <v>0.582</v>
       </c>
       <c r="H2" t="n">
         <v>49.1</v>
       </c>
       <c r="I2" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J2" t="n">
         <v>81.2</v>
       </c>
       <c r="K2" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L2" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M2" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
       <c r="O2" t="n">
         <v>15.2</v>
       </c>
       <c r="P2" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.733</v>
+        <v>0.734</v>
       </c>
       <c r="R2" t="n">
         <v>10.1</v>
@@ -709,10 +776,10 @@
         <v>31.1</v>
       </c>
       <c r="T2" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U2" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="V2" t="n">
         <v>13.9</v>
@@ -730,19 +797,19 @@
         <v>18.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>95.2</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF2" t="n">
         <v>8</v>
@@ -763,13 +830,13 @@
         <v>15</v>
       </c>
       <c r="AL2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AM2" t="n">
         <v>13</v>
       </c>
       <c r="AN2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO2" t="n">
         <v>27</v>
@@ -790,7 +857,7 @@
         <v>23</v>
       </c>
       <c r="AU2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV2" t="n">
         <v>5</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -921,19 +988,19 @@
         <v>1.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AE3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF3" t="n">
         <v>11</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI3" t="n">
         <v>23</v>
@@ -942,7 +1009,7 @@
         <v>30</v>
       </c>
       <c r="AK3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL3" t="n">
         <v>23</v>
@@ -951,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="AN3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO3" t="n">
         <v>22</v>
       </c>
       <c r="AP3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ3" t="n">
         <v>6</v>
@@ -966,7 +1033,7 @@
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT3" t="n">
         <v>30</v>
@@ -978,13 +1045,13 @@
         <v>17</v>
       </c>
       <c r="AW3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX3" t="n">
         <v>7</v>
       </c>
       <c r="AY3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>19</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E4" t="n">
         <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>0.132</v>
+        <v>0.135</v>
       </c>
       <c r="H4" t="n">
         <v>48.2</v>
@@ -1043,19 +1110,19 @@
         <v>33.6</v>
       </c>
       <c r="J4" t="n">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
       <c r="K4" t="n">
         <v>0.416</v>
       </c>
       <c r="L4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="M4" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0.299</v>
+        <v>0.302</v>
       </c>
       <c r="O4" t="n">
         <v>16.6</v>
@@ -1064,22 +1131,22 @@
         <v>22.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.751</v>
+        <v>0.753</v>
       </c>
       <c r="R4" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S4" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="T4" t="n">
-        <v>39.4</v>
+        <v>39.1</v>
       </c>
       <c r="U4" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W4" t="n">
         <v>6.3</v>
@@ -1091,16 +1158,16 @@
         <v>5.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB4" t="n">
         <v>88</v>
       </c>
       <c r="AC4" t="n">
-        <v>-12.7</v>
+        <v>-12.8</v>
       </c>
       <c r="AD4" t="n">
         <v>28</v>
@@ -1121,7 +1188,7 @@
         <v>30</v>
       </c>
       <c r="AJ4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK4" t="n">
         <v>30</v>
@@ -1142,7 +1209,7 @@
         <v>15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AR4" t="n">
         <v>25</v>
@@ -1151,28 +1218,28 @@
         <v>28</v>
       </c>
       <c r="AT4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AU4" t="n">
         <v>19</v>
       </c>
       <c r="AV4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW4" t="n">
         <v>29</v>
       </c>
       <c r="AX4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY4" t="n">
         <v>23</v>
       </c>
       <c r="AZ4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>8</v>
       </c>
       <c r="AD5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1297,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="AH5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI5" t="n">
         <v>9</v>
@@ -1324,13 +1391,13 @@
         <v>20</v>
       </c>
       <c r="AQ5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR5" t="n">
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT5" t="n">
         <v>1</v>
@@ -1342,7 +1409,7 @@
         <v>6</v>
       </c>
       <c r="AW5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX5" t="n">
         <v>3</v>
@@ -1351,7 +1418,7 @@
         <v>19</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA5" t="n">
         <v>28</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1456,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F6" t="n">
         <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>0.34</v>
+        <v>0.327</v>
       </c>
       <c r="H6" t="n">
         <v>48.3</v>
       </c>
       <c r="I6" t="n">
-        <v>34.2</v>
+        <v>34.4</v>
       </c>
       <c r="J6" t="n">
-        <v>81.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.421</v>
+        <v>0.422</v>
       </c>
       <c r="L6" t="n">
         <v>6.8</v>
@@ -1419,31 +1486,31 @@
         <v>19.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="O6" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="P6" t="n">
-        <v>25.4</v>
+        <v>25.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.708</v>
+        <v>0.707</v>
       </c>
       <c r="R6" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="S6" t="n">
         <v>29.6</v>
       </c>
       <c r="T6" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="U6" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V6" t="n">
-        <v>15.3</v>
+        <v>15.5</v>
       </c>
       <c r="W6" t="n">
         <v>7.3</v>
@@ -1455,16 +1522,16 @@
         <v>6.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.09999999999999</v>
+        <v>93.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>-6.4</v>
+        <v>-6.6</v>
       </c>
       <c r="AD6" t="n">
         <v>28</v>
@@ -1482,10 +1549,10 @@
         <v>18</v>
       </c>
       <c r="AI6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AK6" t="n">
         <v>29</v>
@@ -1497,13 +1564,13 @@
         <v>14</v>
       </c>
       <c r="AN6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO6" t="n">
         <v>9</v>
       </c>
       <c r="AP6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ6" t="n">
         <v>28</v>
@@ -1515,19 +1582,19 @@
         <v>24</v>
       </c>
       <c r="AT6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AW6" t="n">
         <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY6" t="n">
         <v>28</v>
@@ -1539,7 +1606,7 @@
         <v>6</v>
       </c>
       <c r="BB6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BC6" t="n">
         <v>28</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -1571,25 +1638,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E7" t="n">
         <v>31</v>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G7" t="n">
-        <v>0.554</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
       </c>
       <c r="I7" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J7" t="n">
-        <v>81.7</v>
+        <v>81.5</v>
       </c>
       <c r="K7" t="n">
         <v>0.44</v>
@@ -1601,13 +1668,13 @@
         <v>22.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0.33</v>
+        <v>0.331</v>
       </c>
       <c r="O7" t="n">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="P7" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="Q7" t="n">
         <v>0.757</v>
@@ -1616,7 +1683,7 @@
         <v>9.9</v>
       </c>
       <c r="S7" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T7" t="n">
         <v>42.4</v>
@@ -1637,40 +1704,40 @@
         <v>4.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AB7" t="n">
         <v>94.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE7" t="n">
         <v>10</v>
       </c>
       <c r="AF7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AI7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ7" t="n">
         <v>14</v>
       </c>
       <c r="AK7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL7" t="n">
         <v>6</v>
@@ -1682,13 +1749,13 @@
         <v>22</v>
       </c>
       <c r="AO7" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AP7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR7" t="n">
         <v>28</v>
@@ -1700,7 +1767,7 @@
         <v>14</v>
       </c>
       <c r="AU7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV7" t="n">
         <v>7</v>
@@ -1715,10 +1782,10 @@
         <v>2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB7" t="n">
         <v>20</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F8" t="n">
         <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>0.545</v>
+        <v>0.537</v>
       </c>
       <c r="H8" t="n">
         <v>48.7</v>
@@ -1771,43 +1838,43 @@
         <v>38.2</v>
       </c>
       <c r="J8" t="n">
-        <v>81.5</v>
+        <v>81.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0.469</v>
+        <v>0.47</v>
       </c>
       <c r="L8" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M8" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0.324</v>
+        <v>0.322</v>
       </c>
       <c r="O8" t="n">
         <v>20.3</v>
       </c>
       <c r="P8" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.736</v>
+        <v>0.738</v>
       </c>
       <c r="R8" t="n">
         <v>11.1</v>
       </c>
       <c r="S8" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T8" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U8" t="n">
         <v>23.6</v>
       </c>
       <c r="V8" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="W8" t="n">
         <v>8.199999999999999</v>
@@ -1819,7 +1886,7 @@
         <v>6.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA8" t="n">
         <v>22.5</v>
@@ -1828,16 +1895,16 @@
         <v>103.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AE8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG8" t="n">
         <v>13</v>
@@ -1849,10 +1916,10 @@
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL8" t="n">
         <v>16</v>
@@ -1864,19 +1931,19 @@
         <v>24</v>
       </c>
       <c r="AO8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP8" t="n">
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR8" t="n">
         <v>17</v>
       </c>
       <c r="AS8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
         <v>7</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E9" t="n">
         <v>21</v>
       </c>
       <c r="F9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>0.382</v>
+        <v>0.389</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
@@ -1959,22 +2026,22 @@
         <v>0.438</v>
       </c>
       <c r="L9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="M9" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0.346</v>
+        <v>0.343</v>
       </c>
       <c r="O9" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="P9" t="n">
         <v>22.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.751</v>
+        <v>0.753</v>
       </c>
       <c r="R9" t="n">
         <v>11.9</v>
@@ -1992,28 +2059,28 @@
         <v>15.8</v>
       </c>
       <c r="W9" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="n">
         <v>5.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>90.40000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="AC9" t="n">
         <v>-5.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AE9" t="n">
         <v>22</v>
@@ -2025,7 +2092,7 @@
         <v>23</v>
       </c>
       <c r="AH9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI9" t="n">
         <v>26</v>
@@ -2043,7 +2110,7 @@
         <v>27</v>
       </c>
       <c r="AN9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AO9" t="n">
         <v>15</v>
@@ -2052,7 +2119,7 @@
         <v>14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR9" t="n">
         <v>11</v>
@@ -2067,19 +2134,19 @@
         <v>27</v>
       </c>
       <c r="AV9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY9" t="n">
         <v>21</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA9" t="n">
         <v>15</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" t="n">
         <v>21</v>
       </c>
       <c r="F10" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G10" t="n">
-        <v>0.389</v>
+        <v>0.396</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
@@ -2135,34 +2202,34 @@
         <v>37.4</v>
       </c>
       <c r="J10" t="n">
-        <v>81.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="K10" t="n">
         <v>0.457</v>
       </c>
       <c r="L10" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M10" t="n">
         <v>20.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.386</v>
+        <v>0.385</v>
       </c>
       <c r="O10" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="P10" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.775</v>
+        <v>0.773</v>
       </c>
       <c r="R10" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="S10" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T10" t="n">
         <v>39.1</v>
@@ -2171,7 +2238,7 @@
         <v>22.2</v>
       </c>
       <c r="V10" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="W10" t="n">
         <v>8.1</v>
@@ -2186,16 +2253,16 @@
         <v>21.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="AB10" t="n">
         <v>97.90000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.4</v>
+        <v>-2.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE10" t="n">
         <v>22</v>
@@ -2216,7 +2283,7 @@
         <v>12</v>
       </c>
       <c r="AK10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL10" t="n">
         <v>3</v>
@@ -2228,22 +2295,22 @@
         <v>2</v>
       </c>
       <c r="AO10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP10" t="n">
         <v>29</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR10" t="n">
         <v>29</v>
       </c>
       <c r="AS10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AU10" t="n">
         <v>7</v>
@@ -2252,16 +2319,16 @@
         <v>4</v>
       </c>
       <c r="AW10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY10" t="n">
         <v>11</v>
       </c>
-      <c r="AX10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>10</v>
-      </c>
       <c r="AZ10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA10" t="n">
         <v>29</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -2299,37 +2366,37 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11" t="n">
         <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>0.545</v>
+        <v>0.537</v>
       </c>
       <c r="H11" t="n">
         <v>48.7</v>
       </c>
       <c r="I11" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="J11" t="n">
-        <v>83.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L11" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M11" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.362</v>
+        <v>0.358</v>
       </c>
       <c r="O11" t="n">
         <v>15.6</v>
@@ -2338,25 +2405,25 @@
         <v>19.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="R11" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S11" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T11" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U11" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V11" t="n">
         <v>14.7</v>
       </c>
       <c r="W11" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X11" t="n">
         <v>4.9</v>
@@ -2371,19 +2438,19 @@
         <v>18.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.40000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AE11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG11" t="n">
         <v>13</v>
@@ -2392,7 +2459,7 @@
         <v>3</v>
       </c>
       <c r="AI11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ11" t="n">
         <v>5</v>
@@ -2404,10 +2471,10 @@
         <v>12</v>
       </c>
       <c r="AM11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO11" t="n">
         <v>21</v>
@@ -2446,7 +2513,7 @@
         <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB11" t="n">
         <v>9</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F12" t="n">
         <v>21</v>
       </c>
       <c r="G12" t="n">
-        <v>0.618</v>
+        <v>0.611</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
@@ -2499,79 +2566,79 @@
         <v>35.5</v>
       </c>
       <c r="J12" t="n">
-        <v>80.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="K12" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L12" t="n">
         <v>5.7</v>
       </c>
       <c r="M12" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0.366</v>
+        <v>0.367</v>
       </c>
       <c r="O12" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="P12" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="Q12" t="n">
         <v>0.779</v>
       </c>
       <c r="R12" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S12" t="n">
         <v>31</v>
       </c>
       <c r="T12" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="U12" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="V12" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W12" t="n">
         <v>7.9</v>
       </c>
       <c r="X12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y12" t="n">
         <v>5.9</v>
       </c>
       <c r="Z12" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>97</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC12" t="n">
         <v>2.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AE12" t="n">
         <v>6</v>
       </c>
       <c r="AF12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG12" t="n">
         <v>6</v>
       </c>
       <c r="AH12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="n">
         <v>21</v>
@@ -2580,7 +2647,7 @@
         <v>21</v>
       </c>
       <c r="AK12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL12" t="n">
         <v>19</v>
@@ -2589,10 +2656,10 @@
         <v>22</v>
       </c>
       <c r="AN12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP12" t="n">
         <v>3</v>
@@ -2601,34 +2668,34 @@
         <v>5</v>
       </c>
       <c r="AR12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS12" t="n">
         <v>12</v>
       </c>
       <c r="AT12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AV12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW12" t="n">
         <v>14</v>
       </c>
       <c r="AX12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ12" t="n">
         <v>28</v>
       </c>
       <c r="BA12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB12" t="n">
         <v>15</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -2741,10 +2808,10 @@
         <v>2.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AE13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF13" t="n">
         <v>7</v>
@@ -2759,7 +2826,7 @@
         <v>14</v>
       </c>
       <c r="AJ13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK13" t="n">
         <v>12</v>
@@ -2783,7 +2850,7 @@
         <v>29</v>
       </c>
       <c r="AR13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS13" t="n">
         <v>23</v>
@@ -2804,7 +2871,7 @@
         <v>22</v>
       </c>
       <c r="AY13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ13" t="n">
         <v>24</v>
@@ -2813,7 +2880,7 @@
         <v>4</v>
       </c>
       <c r="BB13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC13" t="n">
         <v>9</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E14" t="n">
         <v>35</v>
       </c>
       <c r="F14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>0.625</v>
+        <v>0.636</v>
       </c>
       <c r="H14" t="n">
         <v>48.5</v>
@@ -2872,28 +2939,28 @@
         <v>5.5</v>
       </c>
       <c r="M14" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="N14" t="n">
         <v>0.318</v>
       </c>
       <c r="O14" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="P14" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.76</v>
+        <v>0.757</v>
       </c>
       <c r="R14" t="n">
         <v>11.7</v>
       </c>
       <c r="S14" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="T14" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
       <c r="U14" t="n">
         <v>22</v>
@@ -2905,7 +2972,7 @@
         <v>5.9</v>
       </c>
       <c r="X14" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y14" t="n">
         <v>4.3</v>
@@ -2914,16 +2981,16 @@
         <v>17.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>96.7</v>
+        <v>96.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -2944,7 +3011,7 @@
         <v>23</v>
       </c>
       <c r="AK14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AL14" t="n">
         <v>22</v>
@@ -2962,10 +3029,10 @@
         <v>9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AR14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS14" t="n">
         <v>1</v>
@@ -2974,7 +3041,7 @@
         <v>2</v>
       </c>
       <c r="AU14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV14" t="n">
         <v>20</v>
@@ -2983,7 +3050,7 @@
         <v>30</v>
       </c>
       <c r="AX14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
         <v>3</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E15" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F15" t="n">
         <v>23</v>
       </c>
       <c r="G15" t="n">
-        <v>0.574</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
@@ -3054,16 +3121,16 @@
         <v>4</v>
       </c>
       <c r="M15" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0.327</v>
+        <v>0.323</v>
       </c>
       <c r="O15" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P15" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="Q15" t="n">
         <v>0.751</v>
@@ -3093,22 +3160,22 @@
         <v>5.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>95.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF15" t="n">
         <v>8</v>
@@ -3117,16 +3184,16 @@
         <v>10</v>
       </c>
       <c r="AH15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI15" t="n">
         <v>13</v>
       </c>
       <c r="AJ15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL15" t="n">
         <v>28</v>
@@ -3144,7 +3211,7 @@
         <v>13</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR15" t="n">
         <v>7</v>
@@ -3168,7 +3235,7 @@
         <v>12</v>
       </c>
       <c r="AY15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ15" t="n">
         <v>18</v>
@@ -3180,7 +3247,7 @@
         <v>19</v>
       </c>
       <c r="BC15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -3209,43 +3276,43 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E16" t="n">
         <v>39</v>
       </c>
       <c r="F16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>0.722</v>
+        <v>0.736</v>
       </c>
       <c r="H16" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I16" t="n">
-        <v>37.6</v>
+        <v>37.7</v>
       </c>
       <c r="J16" t="n">
         <v>79.09999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.475</v>
+        <v>0.476</v>
       </c>
       <c r="L16" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="M16" t="n">
         <v>15.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0.369</v>
+        <v>0.373</v>
       </c>
       <c r="O16" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="P16" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q16" t="n">
         <v>0.777</v>
@@ -3254,7 +3321,7 @@
         <v>10.2</v>
       </c>
       <c r="S16" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T16" t="n">
         <v>41.6</v>
@@ -3266,7 +3333,7 @@
         <v>15</v>
       </c>
       <c r="W16" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X16" t="n">
         <v>5.5</v>
@@ -3275,28 +3342,28 @@
         <v>4.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>100.3</v>
+        <v>100.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
       </c>
       <c r="AF16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG16" t="n">
         <v>3</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>4</v>
       </c>
       <c r="AH16" t="n">
         <v>5</v>
@@ -3317,13 +3384,13 @@
         <v>23</v>
       </c>
       <c r="AN16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO16" t="n">
         <v>5</v>
       </c>
       <c r="AP16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ16" t="n">
         <v>7</v>
@@ -3347,10 +3414,10 @@
         <v>3</v>
       </c>
       <c r="AX16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ16" t="n">
         <v>17</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F17" t="n">
         <v>28</v>
       </c>
       <c r="G17" t="n">
-        <v>0.491</v>
+        <v>0.481</v>
       </c>
       <c r="H17" t="n">
         <v>48.1</v>
@@ -3409,16 +3476,16 @@
         <v>37.9</v>
       </c>
       <c r="J17" t="n">
-        <v>85.7</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="L17" t="n">
         <v>6.7</v>
       </c>
       <c r="M17" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N17" t="n">
         <v>0.345</v>
@@ -3427,49 +3494,49 @@
         <v>16.4</v>
       </c>
       <c r="P17" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.78</v>
+        <v>0.782</v>
       </c>
       <c r="R17" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S17" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T17" t="n">
         <v>41.9</v>
       </c>
       <c r="U17" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="V17" t="n">
         <v>14</v>
       </c>
       <c r="W17" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y17" t="n">
         <v>4.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AA17" t="n">
         <v>19.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>98.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
@@ -3484,7 +3551,7 @@
         <v>26</v>
       </c>
       <c r="AI17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ17" t="n">
         <v>2</v>
@@ -3496,10 +3563,10 @@
         <v>14</v>
       </c>
       <c r="AM17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN17" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AO17" t="n">
         <v>17</v>
@@ -3526,7 +3593,7 @@
         <v>8</v>
       </c>
       <c r="AW17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX17" t="n">
         <v>20</v>
@@ -3535,13 +3602,13 @@
         <v>9</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA17" t="n">
         <v>18</v>
       </c>
       <c r="BB17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC17" t="n">
         <v>18</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-0.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE18" t="n">
         <v>21</v>
@@ -3675,13 +3742,13 @@
         <v>26</v>
       </c>
       <c r="AL18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM18" t="n">
         <v>6</v>
       </c>
       <c r="AN18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO18" t="n">
         <v>4</v>
@@ -3690,7 +3757,7 @@
         <v>5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AR18" t="n">
         <v>6</v>
@@ -3705,7 +3772,7 @@
         <v>25</v>
       </c>
       <c r="AV18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW18" t="n">
         <v>25</v>
@@ -3723,7 +3790,7 @@
         <v>3</v>
       </c>
       <c r="BB18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC18" t="n">
         <v>21</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -3755,34 +3822,34 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F19" t="n">
         <v>37</v>
       </c>
       <c r="G19" t="n">
-        <v>0.351</v>
+        <v>0.339</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
       </c>
       <c r="I19" t="n">
-        <v>34.1</v>
+        <v>33.9</v>
       </c>
       <c r="J19" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.426</v>
+        <v>0.424</v>
       </c>
       <c r="L19" t="n">
         <v>8</v>
       </c>
       <c r="M19" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="N19" t="n">
         <v>0.345</v>
@@ -3794,19 +3861,19 @@
         <v>22</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.772</v>
+        <v>0.774</v>
       </c>
       <c r="R19" t="n">
         <v>12.2</v>
       </c>
       <c r="S19" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="T19" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="U19" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="V19" t="n">
         <v>15.2</v>
@@ -3821,31 +3888,31 @@
         <v>4.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>93.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5.3</v>
+        <v>-5.6</v>
       </c>
       <c r="AD19" t="n">
         <v>1</v>
       </c>
       <c r="AE19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF19" t="n">
         <v>27</v>
       </c>
       <c r="AG19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI19" t="n">
         <v>29</v>
@@ -3872,10 +3939,10 @@
         <v>16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS19" t="n">
         <v>29</v>
@@ -3884,7 +3951,7 @@
         <v>26</v>
       </c>
       <c r="AU19" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AV19" t="n">
         <v>21</v>
@@ -3896,7 +3963,7 @@
         <v>28</v>
       </c>
       <c r="AY19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ19" t="n">
         <v>10</v>
@@ -3905,10 +3972,10 @@
         <v>16</v>
       </c>
       <c r="BB19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E20" t="n">
         <v>14</v>
       </c>
       <c r="F20" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G20" t="n">
-        <v>0.255</v>
+        <v>0.259</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3967,28 +4034,28 @@
         <v>11.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0.335</v>
+        <v>0.334</v>
       </c>
       <c r="O20" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="P20" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.756</v>
+        <v>0.757</v>
       </c>
       <c r="R20" t="n">
         <v>11.2</v>
       </c>
       <c r="S20" t="n">
-        <v>29.7</v>
+        <v>29.9</v>
       </c>
       <c r="T20" t="n">
-        <v>40.9</v>
+        <v>41.1</v>
       </c>
       <c r="U20" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V20" t="n">
         <v>15.5</v>
@@ -4009,13 +4076,13 @@
         <v>18.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>89.2</v>
+        <v>89</v>
       </c>
       <c r="AC20" t="n">
-        <v>-5</v>
+        <v>-4.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AE20" t="n">
         <v>28</v>
@@ -4027,7 +4094,7 @@
         <v>28</v>
       </c>
       <c r="AH20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
@@ -4045,28 +4112,28 @@
         <v>30</v>
       </c>
       <c r="AN20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO20" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AP20" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
         <v>16</v>
       </c>
       <c r="AS20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AT20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV20" t="n">
         <v>26</v>
@@ -4075,10 +4142,10 @@
         <v>22</v>
       </c>
       <c r="AX20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ20" t="n">
         <v>20</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -4197,25 +4264,25 @@
         <v>2.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AE21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF21" t="n">
         <v>17</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>16</v>
       </c>
       <c r="AG21" t="n">
         <v>17</v>
       </c>
       <c r="AH21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI21" t="n">
         <v>22</v>
       </c>
       <c r="AJ21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK21" t="n">
         <v>23</v>
@@ -4239,13 +4306,13 @@
         <v>21</v>
       </c>
       <c r="AR21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS21" t="n">
         <v>15</v>
       </c>
       <c r="AT21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU21" t="n">
         <v>23</v>
@@ -4257,10 +4324,10 @@
         <v>2</v>
       </c>
       <c r="AX21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ21" t="n">
         <v>25</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -4301,28 +4368,28 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E22" t="n">
         <v>40</v>
       </c>
       <c r="F22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G22" t="n">
-        <v>0.727</v>
+        <v>0.741</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="J22" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="K22" t="n">
-        <v>0.476</v>
+        <v>0.477</v>
       </c>
       <c r="L22" t="n">
         <v>7.1</v>
@@ -4331,16 +4398,16 @@
         <v>19.9</v>
       </c>
       <c r="N22" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O22" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="P22" t="n">
         <v>26.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.798</v>
+        <v>0.799</v>
       </c>
       <c r="R22" t="n">
         <v>10.7</v>
@@ -4352,49 +4419,49 @@
         <v>43.3</v>
       </c>
       <c r="U22" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="V22" t="n">
         <v>16.4</v>
       </c>
       <c r="W22" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X22" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>102.9</v>
+        <v>103</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ22" t="n">
         <v>26</v>
@@ -4430,7 +4497,7 @@
         <v>6</v>
       </c>
       <c r="AU22" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AV22" t="n">
         <v>29</v>
@@ -4442,7 +4509,7 @@
         <v>1</v>
       </c>
       <c r="AY22" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ22" t="n">
         <v>22</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -4561,22 +4628,22 @@
         <v>1.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AE23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF23" t="n">
         <v>8</v>
       </c>
       <c r="AG23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ23" t="n">
         <v>29</v>
@@ -4594,7 +4661,7 @@
         <v>3</v>
       </c>
       <c r="AO23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP23" t="n">
         <v>11</v>
@@ -4612,10 +4679,10 @@
         <v>13</v>
       </c>
       <c r="AU23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW23" t="n">
         <v>28</v>
@@ -4636,7 +4703,7 @@
         <v>21</v>
       </c>
       <c r="BC23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -4743,22 +4810,22 @@
         <v>5.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AE24" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AF24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG24" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH24" t="n">
         <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ24" t="n">
         <v>4</v>
@@ -4773,7 +4840,7 @@
         <v>25</v>
       </c>
       <c r="AN24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4782,7 +4849,7 @@
         <v>30</v>
       </c>
       <c r="AQ24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR24" t="n">
         <v>23</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -4847,28 +4914,28 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E25" t="n">
         <v>28</v>
       </c>
       <c r="F25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G25" t="n">
-        <v>0.509</v>
+        <v>0.519</v>
       </c>
       <c r="H25" t="n">
         <v>48</v>
       </c>
       <c r="I25" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J25" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.454</v>
+        <v>0.455</v>
       </c>
       <c r="L25" t="n">
         <v>6.6</v>
@@ -4880,61 +4947,61 @@
         <v>0.34</v>
       </c>
       <c r="O25" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="P25" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.755</v>
+        <v>0.754</v>
       </c>
       <c r="R25" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S25" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="T25" t="n">
-        <v>41.9</v>
+        <v>41.6</v>
       </c>
       <c r="U25" t="n">
         <v>22.6</v>
       </c>
       <c r="V25" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="W25" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X25" t="n">
         <v>5.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AA25" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AB25" t="n">
         <v>97.09999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AE25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF25" t="n">
         <v>16</v>
       </c>
       <c r="AG25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH25" t="n">
         <v>30</v>
@@ -4943,16 +5010,16 @@
         <v>12</v>
       </c>
       <c r="AJ25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AK25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL25" t="n">
         <v>15</v>
       </c>
       <c r="AM25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN25" t="n">
         <v>18</v>
@@ -4979,19 +5046,19 @@
         <v>6</v>
       </c>
       <c r="AV25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY25" t="n">
         <v>5</v>
       </c>
-      <c r="AY25" t="n">
-        <v>4</v>
-      </c>
       <c r="AZ25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA25" t="n">
         <v>19</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -5029,25 +5096,25 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F26" t="n">
         <v>29</v>
       </c>
       <c r="G26" t="n">
-        <v>0.482</v>
+        <v>0.473</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J26" t="n">
-        <v>81.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="K26" t="n">
         <v>0.446</v>
@@ -5059,28 +5126,28 @@
         <v>20.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0.349</v>
+        <v>0.348</v>
       </c>
       <c r="O26" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P26" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="Q26" t="n">
         <v>0.793</v>
       </c>
       <c r="R26" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S26" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="T26" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U26" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V26" t="n">
         <v>14.1</v>
@@ -5089,25 +5156,25 @@
         <v>8.1</v>
       </c>
       <c r="X26" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y26" t="n">
         <v>4.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.3</v>
+        <v>97.2</v>
       </c>
       <c r="AC26" t="n">
         <v>1.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE26" t="n">
         <v>19</v>
@@ -5119,16 +5186,16 @@
         <v>20</v>
       </c>
       <c r="AH26" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AI26" t="n">
         <v>15</v>
       </c>
       <c r="AJ26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AK26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL26" t="n">
         <v>10</v>
@@ -5137,7 +5204,7 @@
         <v>9</v>
       </c>
       <c r="AN26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO26" t="n">
         <v>12</v>
@@ -5152,19 +5219,19 @@
         <v>18</v>
       </c>
       <c r="AS26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV26" t="n">
         <v>9</v>
       </c>
       <c r="AW26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX26" t="n">
         <v>14</v>
@@ -5173,16 +5240,16 @@
         <v>8</v>
       </c>
       <c r="AZ26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -5289,19 +5356,19 @@
         <v>-5.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AE27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF27" t="n">
         <v>26</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AG27" t="n">
         <v>25</v>
       </c>
-      <c r="AG27" t="n">
-        <v>26</v>
-      </c>
       <c r="AH27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI27" t="n">
         <v>11</v>
@@ -5346,7 +5413,7 @@
         <v>16</v>
       </c>
       <c r="AW27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX27" t="n">
         <v>18</v>
@@ -5355,7 +5422,7 @@
         <v>29</v>
       </c>
       <c r="AZ27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA27" t="n">
         <v>9</v>
@@ -5364,7 +5431,7 @@
         <v>8</v>
       </c>
       <c r="BC27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5460,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E28" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F28" t="n">
         <v>14</v>
       </c>
       <c r="G28" t="n">
-        <v>0.736</v>
+        <v>0.731</v>
       </c>
       <c r="H28" t="n">
         <v>48.4</v>
       </c>
       <c r="I28" t="n">
-        <v>39.2</v>
+        <v>39</v>
       </c>
       <c r="J28" t="n">
         <v>83</v>
       </c>
       <c r="K28" t="n">
-        <v>0.472</v>
+        <v>0.47</v>
       </c>
       <c r="L28" t="n">
         <v>8.199999999999999</v>
@@ -5423,28 +5490,28 @@
         <v>21.2</v>
       </c>
       <c r="N28" t="n">
-        <v>0.389</v>
+        <v>0.387</v>
       </c>
       <c r="O28" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="P28" t="n">
         <v>21.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.731</v>
+        <v>0.729</v>
       </c>
       <c r="R28" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S28" t="n">
         <v>32.3</v>
       </c>
       <c r="T28" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U28" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="V28" t="n">
         <v>13.3</v>
@@ -5453,37 +5520,37 @@
         <v>7.3</v>
       </c>
       <c r="X28" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y28" t="n">
         <v>5</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB28" t="n">
-        <v>102.1</v>
+        <v>101.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AD28" t="n">
         <v>28</v>
       </c>
       <c r="AE28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF28" t="n">
         <v>2</v>
       </c>
       <c r="AG28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
@@ -5492,7 +5559,7 @@
         <v>6</v>
       </c>
       <c r="AK28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL28" t="n">
         <v>2</v>
@@ -5531,13 +5598,13 @@
         <v>21</v>
       </c>
       <c r="AX28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY28" t="n">
         <v>17</v>
       </c>
       <c r="AZ28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA28" t="n">
         <v>21</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -5575,58 +5642,58 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E29" t="n">
         <v>20</v>
       </c>
       <c r="F29" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G29" t="n">
-        <v>0.357</v>
+        <v>0.364</v>
       </c>
       <c r="H29" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I29" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="J29" t="n">
-        <v>78.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L29" t="n">
         <v>5.5</v>
       </c>
       <c r="M29" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0.335</v>
+        <v>0.337</v>
       </c>
       <c r="O29" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="P29" t="n">
         <v>21.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.771</v>
+        <v>0.774</v>
       </c>
       <c r="R29" t="n">
         <v>10.5</v>
       </c>
       <c r="S29" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="T29" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="U29" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V29" t="n">
         <v>15.1</v>
@@ -5635,37 +5702,37 @@
         <v>6.8</v>
       </c>
       <c r="X29" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y29" t="n">
         <v>4.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="AA29" t="n">
         <v>18.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>91.7</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="AC29" t="n">
         <v>-3.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE29" t="n">
         <v>24</v>
       </c>
       <c r="AF29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG29" t="n">
         <v>24</v>
       </c>
       <c r="AH29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI29" t="n">
         <v>25</v>
@@ -5683,7 +5750,7 @@
         <v>20</v>
       </c>
       <c r="AN29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO29" t="n">
         <v>14</v>
@@ -5692,7 +5759,7 @@
         <v>17</v>
       </c>
       <c r="AQ29" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AR29" t="n">
         <v>22</v>
@@ -5710,13 +5777,13 @@
         <v>19</v>
       </c>
       <c r="AW29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY29" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F30" t="n">
         <v>27</v>
       </c>
       <c r="G30" t="n">
-        <v>0.518</v>
+        <v>0.509</v>
       </c>
       <c r="H30" t="n">
         <v>48.8</v>
@@ -5775,19 +5842,19 @@
         <v>38.2</v>
       </c>
       <c r="J30" t="n">
-        <v>83.90000000000001</v>
+        <v>84</v>
       </c>
       <c r="K30" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L30" t="n">
         <v>3.8</v>
       </c>
       <c r="M30" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="N30" t="n">
-        <v>0.308</v>
+        <v>0.307</v>
       </c>
       <c r="O30" t="n">
         <v>18.8</v>
@@ -5796,19 +5863,19 @@
         <v>25</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.752</v>
+        <v>0.75</v>
       </c>
       <c r="R30" t="n">
         <v>13.1</v>
       </c>
       <c r="S30" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="T30" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="U30" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V30" t="n">
         <v>14.2</v>
@@ -5820,31 +5887,31 @@
         <v>5.7</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>99.09999999999999</v>
+        <v>99</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH30" t="n">
         <v>2</v>
@@ -5856,7 +5923,7 @@
         <v>3</v>
       </c>
       <c r="AK30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL30" t="n">
         <v>30</v>
@@ -5874,13 +5941,13 @@
         <v>8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AR30" t="n">
         <v>3</v>
       </c>
       <c r="AS30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT30" t="n">
         <v>4</v>
@@ -5889,7 +5956,7 @@
         <v>11</v>
       </c>
       <c r="AV30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW30" t="n">
         <v>7</v>
@@ -5898,7 +5965,7 @@
         <v>4</v>
       </c>
       <c r="AY30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ30" t="n">
         <v>29</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E31" t="n">
         <v>12</v>
       </c>
       <c r="F31" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G31" t="n">
-        <v>0.214</v>
+        <v>0.218</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
@@ -5957,43 +6024,43 @@
         <v>36.2</v>
       </c>
       <c r="J31" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="K31" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L31" t="n">
         <v>5.2</v>
       </c>
       <c r="M31" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="N31" t="n">
-        <v>0.323</v>
+        <v>0.321</v>
       </c>
       <c r="O31" t="n">
         <v>15.6</v>
       </c>
       <c r="P31" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.726</v>
+        <v>0.725</v>
       </c>
       <c r="R31" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="S31" t="n">
-        <v>29.5</v>
+        <v>29.6</v>
       </c>
       <c r="T31" t="n">
         <v>41.4</v>
       </c>
       <c r="U31" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="V31" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="W31" t="n">
         <v>7.8</v>
@@ -6002,22 +6069,22 @@
         <v>6.3</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AA31" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>93.3</v>
+        <v>93.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7</v>
+        <v>-6.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6035,7 +6102,7 @@
         <v>18</v>
       </c>
       <c r="AJ31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK31" t="n">
         <v>25</v>
@@ -6053,16 +6120,16 @@
         <v>20</v>
       </c>
       <c r="AP31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR31" t="n">
         <v>12</v>
       </c>
       <c r="AS31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT31" t="n">
         <v>22</v>
@@ -6071,7 +6138,7 @@
         <v>28</v>
       </c>
       <c r="AV31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW31" t="n">
         <v>15</v>
@@ -6080,16 +6147,16 @@
         <v>2</v>
       </c>
       <c r="AY31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA31" t="n">
         <v>22</v>
       </c>
       <c r="BB31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC31" t="n">
         <v>29</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-6-2011-12</t>
+          <t>2012-04-06</t>
         </is>
       </c>
     </row>
